--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260812.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260812.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.81%</t>
+          <t>3.80%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>3.69%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.42%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.19%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>4,413,802,069</t>
+          <t>4,472,762,318</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
@@ -770,29 +770,29 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>30,987,000</t>
+          <t>20,089,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.71%</t>
         </is>
       </c>
     </row>
@@ -814,51 +814,51 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>3,801,000</t>
+          <t>30,987,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>20,089,000</t>
+          <t>3,801,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.63%</t>
         </is>
       </c>
     </row>
@@ -880,46 +880,46 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.53%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>25,898,000</t>
+          <t>9,520,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>34,365,000</t>
+          <t>25,898,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -931,110 +931,110 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>6,485,000</t>
+          <t>20,683,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>4,126,000</t>
+          <t>34,365,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>9,520,000</t>
+          <t>6,485,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.40%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>2,820,000</t>
+          <t>4,126,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>20,683,000</t>
+          <t>2,820,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.23%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.17%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
@@ -1122,95 +1122,95 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>17,369,000</t>
+          <t>40,734,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>40,734,000</t>
+          <t>15,056,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>6,546,000</t>
+          <t>17,369,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>5,975,000</t>
+          <t>6,546,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
@@ -1227,34 +1227,34 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2,547,385,322</t>
+          <t>2,599,105,322</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>15,056,000</t>
+          <t>5,975,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
@@ -1320,73 +1320,73 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.68%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>14,134,000</t>
+          <t>4,886,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>至上電子</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>22,613,000</t>
+          <t>14,134,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>至上電子</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>4,886,000</t>
+          <t>22,613,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
@@ -1408,46 +1408,46 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>16,505,000</t>
+          <t>23,205,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>13,785,000</t>
+          <t>16,505,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,88 +1459,88 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>23,205,000</t>
+          <t>13,785,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>7,223,000</t>
+          <t>8,951,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>8,715,000</t>
+          <t>7,223,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>8,951,000</t>
+          <t>8,715,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -1562,51 +1562,51 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>1,575,000</t>
+          <t>2,088,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>2,088,000</t>
+          <t>1,575,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -1650,51 +1650,51 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>原相科技</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>6,330,000</t>
+          <t>48,929,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>原相科技</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>48,929,000</t>
+          <t>6,330,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-27,532,786</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
